--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20260730120000</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -2563,7 +2563,7 @@
     <t>Practitioner.qualification:degree.code.coding:degree</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS|20260223120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS|20260730120000</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.text</t>
@@ -2799,7 +2799,7 @@
     <t>Compétence acquise par le professionnel (competence) R39 ou Compétence exclusive exercée par le professionnel à titre exclusif (competenceExclusive) R40 ou Diplôme d'études spécialisées complémentaires (DESC)DESCnonQualifian R42 ou Capacité (savoir-faire)de médecine (capaciteSavoirFaire) R43 ou Qualification de praticien adjoint contractuel (qualificationPAC) R44 ou Fonction qualifiée (Synonyme: fonctionQualifiee) R45 ou Droit d'exercice complémentaire (Synonyme: droitExerciceComplementaire) R97 ou Orientation particulière (Synonyme: orientationParticuliere) G13 ou Activité ponctuelle du professionnel de type expertise (attributionParticuliere) G13.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20260730120000</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.code.text</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
